--- a/results/summary.xlsx
+++ b/results/summary.xlsx
@@ -527,55 +527,55 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>26.42865138790538</v>
+        <v>23.34944528885896</v>
       </c>
       <c r="D2" t="n">
-        <v>16.91267188022946</v>
+        <v>14.05693888683988</v>
       </c>
       <c r="E2" t="n">
-        <v>26.61290322580645</v>
+        <v>28.36021505376344</v>
       </c>
       <c r="F2" t="n">
-        <v>263.939575</v>
+        <v>328.9534857142857</v>
       </c>
       <c r="G2" t="n">
-        <v>8.182000000000002</v>
+        <v>9.775675</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4293719422043011</v>
+        <v>0.5806249615975423</v>
       </c>
       <c r="I2" t="n">
-        <v>717.2880250000001</v>
+        <v>659.27585</v>
       </c>
       <c r="J2" t="n">
-        <v>99.738625</v>
+        <v>156.7389142857143</v>
       </c>
       <c r="K2" t="n">
-        <v>2.469135802469136</v>
+        <v>44.55958549222798</v>
       </c>
       <c r="L2" t="n">
-        <v>2.023121387283237</v>
+        <v>11.56862745098039</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O2" t="n">
-        <v>1117.575425795201</v>
+        <v>1100.166276861463</v>
       </c>
       <c r="P2" t="n">
-        <v>1270.444180068849</v>
+        <v>1219.577581115558</v>
       </c>
       <c r="Q2" t="n">
-        <v>1040.9427713453</v>
+        <v>1000.584249026128</v>
       </c>
       <c r="R2" t="n">
-        <v>809.9525247441618</v>
+        <v>790.7877668759913</v>
       </c>
       <c r="S2" t="n">
-        <v>1958.653584715191</v>
+        <v>1993.618822993257</v>
       </c>
     </row>
     <row r="3">
@@ -588,55 +588,55 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>25.66524997893208</v>
+        <v>26.7994785213956</v>
       </c>
       <c r="D3" t="n">
-        <v>16.43697666219747</v>
+        <v>15.97369446048375</v>
       </c>
       <c r="E3" t="n">
-        <v>26.20967741935484</v>
+        <v>25.67204301075269</v>
       </c>
       <c r="F3" t="n">
-        <v>260.288175</v>
+        <v>245.8346464285715</v>
       </c>
       <c r="G3" t="n">
-        <v>7.7394</v>
+        <v>8.261150000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4116069220430107</v>
+        <v>0.5120759984639017</v>
       </c>
       <c r="I3" t="n">
-        <v>727.1259499999999</v>
+        <v>745.3666928571428</v>
       </c>
       <c r="J3" t="n">
-        <v>88.30302500000002</v>
+        <v>182.4132607142857</v>
       </c>
       <c r="K3" t="n">
-        <v>11.51960784313725</v>
+        <v>43.95886889460154</v>
       </c>
       <c r="L3" t="n">
-        <v>8.136482939632545</v>
+        <v>10.03861003861004</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
-        <v>1407.646797365715</v>
+        <v>1134.257271086604</v>
       </c>
       <c r="P3" t="n">
-        <v>843.9340477320402</v>
+        <v>1488.232976306936</v>
       </c>
       <c r="Q3" t="n">
-        <v>1101.162513941505</v>
+        <v>1276.809285239969</v>
       </c>
       <c r="R3" t="n">
-        <v>1066.312800667794</v>
+        <v>806.08516640582</v>
       </c>
       <c r="S3" t="n">
-        <v>2005.69316961349</v>
+        <v>2147.463775721239</v>
       </c>
     </row>
     <row r="4">
@@ -649,55 +649,55 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>26.47166771272644</v>
+        <v>22.39798671381331</v>
       </c>
       <c r="D4" t="n">
-        <v>16.8843705053516</v>
+        <v>12.18235560626872</v>
       </c>
       <c r="E4" t="n">
-        <v>24.86559139784946</v>
+        <v>29.97311827956989</v>
       </c>
       <c r="F4" t="n">
-        <v>259.298075</v>
+        <v>323.3304142857143</v>
       </c>
       <c r="G4" t="n">
-        <v>9.009125000000001</v>
+        <v>8.247425</v>
       </c>
       <c r="H4" t="n">
-        <v>0.473146001344086</v>
+        <v>0.5768867895545315</v>
       </c>
       <c r="I4" t="n">
-        <v>719.5371499999999</v>
+        <v>681.5153071428571</v>
       </c>
       <c r="J4" t="n">
-        <v>140.1143</v>
+        <v>135.8011035714286</v>
       </c>
       <c r="K4" t="n">
-        <v>19.559902200489</v>
+        <v>31.18556701030928</v>
       </c>
       <c r="L4" t="n">
-        <v>6.796116504854369</v>
+        <v>5.387931034482759</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O4" t="n">
-        <v>1363.905366099601</v>
+        <v>1490.078742722848</v>
       </c>
       <c r="P4" t="n">
-        <v>1285.108299241414</v>
+        <v>1052.874371391239</v>
       </c>
       <c r="Q4" t="n">
-        <v>1387.894197909765</v>
+        <v>1439.872226044444</v>
       </c>
       <c r="R4" t="n">
-        <v>991.0810626377778</v>
+        <v>1148.641203775594</v>
       </c>
       <c r="S4" t="n">
-        <v>2364.33766851863</v>
+        <v>1924.296646749696</v>
       </c>
     </row>
     <row r="5">
@@ -710,55 +710,55 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>24.47193260879757</v>
+        <v>20.93104187173977</v>
       </c>
       <c r="D5" t="n">
-        <v>15.81779486662763</v>
+        <v>11.42777834052015</v>
       </c>
       <c r="E5" t="n">
-        <v>22.04301075268817</v>
+        <v>20.43010752688172</v>
       </c>
       <c r="F5" t="n">
-        <v>194.2516000000001</v>
+        <v>221.119275</v>
       </c>
       <c r="G5" t="n">
-        <v>5.338825</v>
+        <v>6.004425000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3566331653225808</v>
+        <v>0.5045465581797236</v>
       </c>
       <c r="I5" t="n">
-        <v>578.7723999999999</v>
+        <v>542.0363357142857</v>
       </c>
       <c r="J5" t="n">
-        <v>96.55272500000001</v>
+        <v>197.2056214285714</v>
       </c>
       <c r="K5" t="n">
-        <v>1.449275362318841</v>
+        <v>54.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1.492537313432836</v>
+        <v>16.48550724637681</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>733.4051415202343</v>
+        <v>774.5008374902231</v>
       </c>
       <c r="P5" t="n">
-        <v>760.2860332110156</v>
+        <v>963.4491979892412</v>
       </c>
       <c r="Q5" t="n">
-        <v>885.45243938125</v>
+        <v>694.7143052696429</v>
       </c>
       <c r="R5" t="n">
-        <v>569.2247758039521</v>
+        <v>551.3194941214985</v>
       </c>
       <c r="S5" t="n">
-        <v>908.3985156425888</v>
+        <v>1457.312596197024</v>
       </c>
     </row>
     <row r="6">
@@ -771,55 +771,55 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>26.27181475454845</v>
+        <v>27.30342016474724</v>
       </c>
       <c r="D6" t="n">
-        <v>17.71300817523483</v>
+        <v>16.18130030491545</v>
       </c>
       <c r="E6" t="n">
-        <v>19.48924731182796</v>
+        <v>17.33870967741936</v>
       </c>
       <c r="F6" t="n">
-        <v>147.04285</v>
+        <v>145.8716107142857</v>
       </c>
       <c r="G6" t="n">
-        <v>5.088075</v>
+        <v>5.620975</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2898193548387097</v>
+        <v>0.48365</v>
       </c>
       <c r="I6" t="n">
-        <v>612.8190999999999</v>
+        <v>614.5379785714285</v>
       </c>
       <c r="J6" t="n">
-        <v>107.86175</v>
+        <v>255.8227928571429</v>
       </c>
       <c r="K6" t="n">
-        <v>11.08433734939759</v>
+        <v>51.99004975124378</v>
       </c>
       <c r="L6" t="n">
-        <v>9.066666666666666</v>
+        <v>13.02752293577982</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>938.3424255663281</v>
+        <v>920.7545315996058</v>
       </c>
       <c r="P6" t="n">
-        <v>654.2547890961719</v>
+        <v>1150.531440219144</v>
       </c>
       <c r="Q6" t="n">
-        <v>695.4769495312501</v>
+        <v>1050.005743589286</v>
       </c>
       <c r="R6" t="n">
-        <v>722.9606378699623</v>
+        <v>660.3860226069012</v>
       </c>
       <c r="S6" t="n">
-        <v>1215.47545139733</v>
+        <v>1682.93055832744</v>
       </c>
     </row>
     <row r="7">
@@ -832,55 +832,55 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>25.09153793098832</v>
+        <v>23.08788559719676</v>
       </c>
       <c r="D7" t="n">
-        <v>16.24491377543634</v>
+        <v>13.24023995894731</v>
       </c>
       <c r="E7" t="n">
-        <v>17.74193548387097</v>
+        <v>23.25268817204301</v>
       </c>
       <c r="F7" t="n">
-        <v>161.449425</v>
+        <v>206.057325</v>
       </c>
       <c r="G7" t="n">
-        <v>5.373699999999999</v>
+        <v>5.734375</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3577832661290323</v>
+        <v>0.4758362471198158</v>
       </c>
       <c r="I7" t="n">
-        <v>600.0540749999999</v>
+        <v>570.1100285714285</v>
       </c>
       <c r="J7" t="n">
-        <v>140.973625</v>
+        <v>181.1544464285714</v>
       </c>
       <c r="K7" t="n">
-        <v>12.07729468599034</v>
+        <v>33.16708229426434</v>
       </c>
       <c r="L7" t="n">
-        <v>5.54089709762533</v>
+        <v>7.67590618336887</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O7" t="n">
-        <v>952.7621807664843</v>
+        <v>942.8942145216629</v>
       </c>
       <c r="P7" t="n">
-        <v>946.6644956022657</v>
+        <v>880.8933225729797</v>
       </c>
       <c r="Q7" t="n">
-        <v>1018.1780836375</v>
+        <v>892.1824350080356</v>
       </c>
       <c r="R7" t="n">
-        <v>710.1147876249704</v>
+        <v>704.2685922181304</v>
       </c>
       <c r="S7" t="n">
-        <v>1473.711750648655</v>
+        <v>1443.362008513663</v>
       </c>
     </row>
     <row r="8">
@@ -893,34 +893,34 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>3.027996114971929</v>
+        <v>2.20024928384126</v>
       </c>
       <c r="D8" t="n">
-        <v>1.729621100788614</v>
+        <v>1.936029020594409</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>1.88325</v>
+        <v>5.585700000000004</v>
       </c>
       <c r="G8" t="n">
-        <v>1.88325</v>
+        <v>2.392100000000003</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004785000000000004</v>
+        <v>0.00984409722222223</v>
       </c>
       <c r="I8" t="n">
-        <v>7.0565</v>
+        <v>5.725514285714286</v>
       </c>
       <c r="J8" t="n">
-        <v>3.06195</v>
+        <v>4.456585714285713</v>
       </c>
       <c r="K8" t="n">
-        <v>1.955307262569832</v>
+        <v>10.06993006993007</v>
       </c>
       <c r="L8" t="n">
-        <v>72.22222222222223</v>
+        <v>86.84210526315789</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -929,19 +929,19 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>9.46906425640625</v>
+        <v>11.22510128164062</v>
       </c>
       <c r="P8" t="n">
-        <v>16.97943179359375</v>
+        <v>16.79714573710937</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.4613193</v>
+        <v>5.043491447321423</v>
       </c>
       <c r="R8" t="n">
-        <v>4.468402401922331</v>
+        <v>2.93084410789568</v>
       </c>
       <c r="S8" t="n">
-        <v>40.53755428843294</v>
+        <v>71.71747045580885</v>
       </c>
     </row>
     <row r="9">
@@ -954,34 +954,34 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>2.736635388805798</v>
+        <v>4.746531400428134</v>
       </c>
       <c r="D9" t="n">
-        <v>1.577819494704957</v>
+        <v>3.437988746186372</v>
       </c>
       <c r="E9" t="n">
         <v>0.1388888888888889</v>
       </c>
       <c r="F9" t="n">
-        <v>2.274950000000002</v>
+        <v>1.369100000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>2.274950000000002</v>
+        <v>1.369100000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005032847222222224</v>
+        <v>0.01344427083333333</v>
       </c>
       <c r="I9" t="n">
-        <v>6.6648</v>
+        <v>8.287200000000002</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3487</v>
+        <v>14.810775</v>
       </c>
       <c r="K9" t="n">
-        <v>10.47486033519553</v>
+        <v>21.81818181818182</v>
       </c>
       <c r="L9" t="n">
-        <v>91.13924050632912</v>
+        <v>88.81987577639751</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -990,19 +990,19 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>15.12775496554687</v>
+        <v>38.87885555835936</v>
       </c>
       <c r="P9" t="n">
-        <v>12.78181680945313</v>
+        <v>23.07005793539063</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.999424025000001</v>
+        <v>18.49075213124999</v>
       </c>
       <c r="R9" t="n">
-        <v>12.09911591853806</v>
+        <v>19.39161882727043</v>
       </c>
       <c r="S9" t="n">
-        <v>15.15863550454128</v>
+        <v>155.9935117525301</v>
       </c>
     </row>
     <row r="10">
@@ -1015,34 +1015,34 @@
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>3.4471107151105</v>
+        <v>2.796483165151353</v>
       </c>
       <c r="D10" t="n">
-        <v>1.943978327130965</v>
+        <v>1.586996063604083</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="F10" t="n">
-        <v>1.939175000000001</v>
+        <v>2.793824999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>1.939175000000001</v>
+        <v>1.995100000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>0.012138125</v>
+        <v>0.009519375</v>
       </c>
       <c r="I10" t="n">
-        <v>7.000575</v>
+        <v>8.026799999999998</v>
       </c>
       <c r="J10" t="n">
-        <v>9.300274999999999</v>
+        <v>8.060124999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>15.36312849162011</v>
+        <v>13.98601398601399</v>
       </c>
       <c r="L10" t="n">
-        <v>92.10526315789474</v>
+        <v>89.52380952380952</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1051,19 +1051,19 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>52.50094775320312</v>
+        <v>15.40481776601562</v>
       </c>
       <c r="P10" t="n">
-        <v>46.72598949054687</v>
+        <v>27.90599292148437</v>
       </c>
       <c r="Q10" t="n">
-        <v>55.16705549374999</v>
+        <v>8.839762437499996</v>
       </c>
       <c r="R10" t="n">
-        <v>41.39827276238897</v>
+        <v>7.257462103276382</v>
       </c>
       <c r="S10" t="n">
-        <v>58.5258021549384</v>
+        <v>66.0687388613768</v>
       </c>
     </row>
   </sheetData>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26.1885230265213</v>
+        <v>24.18230350802262</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4536778733862398</v>
+        <v>2.315927922664015</v>
       </c>
     </row>
     <row r="3">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.74467301592617</v>
+        <v>14.07099631786412</v>
       </c>
       <c r="D3" t="n">
-        <v>0.266848321202234</v>
+        <v>1.895708518046852</v>
       </c>
     </row>
     <row r="4">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25.89605734767025</v>
+        <v>28.00179211469534</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9149004416067261</v>
+        <v>2.172823593724398</v>
       </c>
     </row>
     <row r="5">
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>261.175275</v>
+        <v>299.3728488095238</v>
       </c>
       <c r="D5" t="n">
-        <v>2.444604338129154</v>
+        <v>46.45060891646699</v>
       </c>
     </row>
     <row r="6">
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8.310175000000001</v>
+        <v>8.761416666666667</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6444936127495761</v>
+        <v>0.8784002897075642</v>
       </c>
     </row>
     <row r="7">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.4380416218637992</v>
+        <v>0.5565292498719918</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03167233934136766</v>
+        <v>0.03854299097266502</v>
       </c>
     </row>
     <row r="8">
@@ -1222,10 +1222,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>721.3170416666666</v>
+        <v>695.38595</v>
       </c>
       <c r="D8" t="n">
-        <v>5.154823259356966</v>
+        <v>44.69009236862371</v>
       </c>
     </row>
     <row r="9">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>109.3853166666667</v>
+        <v>158.3177595238095</v>
       </c>
       <c r="D9" t="n">
-        <v>27.21940574967074</v>
+        <v>23.34615305766655</v>
       </c>
     </row>
     <row r="10">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11.18288194869846</v>
+        <v>39.90134046571293</v>
       </c>
       <c r="D10" t="n">
-        <v>8.550357434862615</v>
+        <v>7.554054891388148</v>
       </c>
     </row>
     <row r="11">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5.651906943923383</v>
+        <v>8.998389508024397</v>
       </c>
       <c r="D11" t="n">
-        <v>3.213286325077505</v>
+        <v>3.218974388282016</v>
       </c>
     </row>
     <row r="12">
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1.527525231651947</v>
       </c>
     </row>
     <row r="14">
@@ -1330,10 +1330,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1296.375863086839</v>
+        <v>1241.500763556972</v>
       </c>
       <c r="D14" t="n">
-        <v>156.3826252627279</v>
+        <v>215.9486229788412</v>
       </c>
     </row>
     <row r="15">
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1133.162175680768</v>
+        <v>1253.561642937911</v>
       </c>
       <c r="D15" t="n">
-        <v>250.5861959392834</v>
+        <v>219.659887239329</v>
       </c>
     </row>
     <row r="16">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1176.666494398857</v>
+        <v>1239.088586770181</v>
       </c>
       <c r="D16" t="n">
-        <v>185.3900250753999</v>
+        <v>222.0599468792103</v>
       </c>
     </row>
     <row r="17">
@@ -1384,10 +1384,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>955.7821293499113</v>
+        <v>915.1713790191349</v>
       </c>
       <c r="D17" t="n">
-        <v>131.775030967009</v>
+        <v>202.3354193213645</v>
       </c>
     </row>
     <row r="18">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2109.561474282437</v>
+        <v>2021.793081821397</v>
       </c>
       <c r="D18" t="n">
-        <v>221.892682391646</v>
+        <v>114.2201099138702</v>
       </c>
     </row>
     <row r="19">
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>25.27842843144478</v>
+        <v>23.77411587789459</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9143795596024971</v>
+        <v>3.241139502691633</v>
       </c>
     </row>
     <row r="20">
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.59190560576627</v>
+        <v>13.6164395347943</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9941131067525694</v>
+        <v>2.398986735508918</v>
       </c>
     </row>
     <row r="21">
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>19.75806451612903</v>
+        <v>20.34050179211469</v>
       </c>
       <c r="D21" t="n">
-        <v>2.163101739170844</v>
+        <v>2.958007319040155</v>
       </c>
     </row>
     <row r="22">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>167.5812916666667</v>
+        <v>191.0160702380953</v>
       </c>
       <c r="D22" t="n">
-        <v>24.19434563599435</v>
+        <v>39.81497524453936</v>
       </c>
     </row>
     <row r="23">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5.266866666666666</v>
+        <v>5.786591666666666</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1558169164703666</v>
+        <v>0.1969858137870178</v>
       </c>
     </row>
     <row r="24">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.3347452620967743</v>
+        <v>0.4880109350998465</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03891122640301141</v>
+        <v>0.01484364532377311</v>
       </c>
     </row>
     <row r="25">
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>597.2151916666667</v>
+        <v>575.5614476190475</v>
       </c>
       <c r="D25" t="n">
-        <v>17.19996770804259</v>
+        <v>36.55694915430898</v>
       </c>
     </row>
     <row r="26">
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>115.1293666666667</v>
+        <v>211.3942869047619</v>
       </c>
       <c r="D26" t="n">
-        <v>23.0850119820785</v>
+        <v>39.30431478337614</v>
       </c>
     </row>
     <row r="27">
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8.20363579923559</v>
+        <v>46.46904401516937</v>
       </c>
       <c r="D27" t="n">
-        <v>5.870479516352391</v>
+        <v>11.57512345506649</v>
       </c>
     </row>
     <row r="28">
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.366700359241611</v>
+        <v>12.39631212184183</v>
       </c>
       <c r="D28" t="n">
-        <v>3.790068237199328</v>
+        <v>4.438590771975026</v>
       </c>
     </row>
     <row r="29">
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>2.081665999466133</v>
       </c>
     </row>
     <row r="31">
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>874.8365826176823</v>
+        <v>879.3831945371639</v>
       </c>
       <c r="D31" t="n">
-        <v>122.6952392441686</v>
+        <v>91.50285790489707</v>
       </c>
     </row>
     <row r="32">
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>787.0684393031511</v>
+        <v>998.291320260455</v>
       </c>
       <c r="D32" t="n">
-        <v>148.0332127321704</v>
+        <v>138.1544741773258</v>
       </c>
     </row>
     <row r="33">
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>866.3691575166667</v>
+        <v>878.9674946223213</v>
       </c>
       <c r="D33" t="n">
-        <v>162.1947416638632</v>
+        <v>178.0139812566941</v>
       </c>
     </row>
     <row r="34">
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>667.4334004329615</v>
+        <v>638.65803631551</v>
       </c>
       <c r="D34" t="n">
-        <v>85.29334341418713</v>
+        <v>78.75554388963641</v>
       </c>
     </row>
     <row r="35">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1199.195239229525</v>
+        <v>1527.868387679376</v>
       </c>
       <c r="D35" t="n">
-        <v>283.0080341605652</v>
+        <v>134.4688153392633</v>
       </c>
     </row>
     <row r="36">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3.070580739629408</v>
+        <v>3.247754616473582</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3571468675697116</v>
+        <v>1.331774228762663</v>
       </c>
     </row>
     <row r="37">
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.750472974208179</v>
+        <v>2.320337943461621</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1839678589040039</v>
+        <v>0.9835209651501141</v>
       </c>
     </row>
     <row r="38">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="C38" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="D38" t="n">
         <v>0.1388888888888889</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2.032458333333334</v>
+        <v>3.249541666666668</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2118573994656162</v>
+        <v>2.144921245689067</v>
       </c>
     </row>
     <row r="40">
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.032458333333334</v>
+        <v>1.918766666666668</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2118573994656162</v>
+        <v>0.515754140393787</v>
       </c>
     </row>
     <row r="41">
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.00731865740740741</v>
+        <v>0.01093591435185185</v>
       </c>
       <c r="D41" t="n">
-        <v>0.00417562066864658</v>
+        <v>0.002178359545401962</v>
       </c>
     </row>
     <row r="42">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6.907291666666666</v>
+        <v>7.346504761904762</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2118573994656154</v>
+        <v>1.409843832814532</v>
       </c>
     </row>
     <row r="43">
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4.903641666666666</v>
+        <v>9.109161904761903</v>
       </c>
       <c r="D43" t="n">
-        <v>3.824260698678678</v>
+        <v>5.256202789254277</v>
       </c>
     </row>
     <row r="44">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>9.264432029795158</v>
+        <v>15.29137529137529</v>
       </c>
       <c r="D44" t="n">
-        <v>6.785371768696882</v>
+        <v>5.981916991084545</v>
       </c>
     </row>
     <row r="45">
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>85.15557529548202</v>
+        <v>88.39526352112163</v>
       </c>
       <c r="D45" t="n">
-        <v>11.2110220867249</v>
+        <v>1.390361863292114</v>
       </c>
     </row>
     <row r="46">
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>25.69925565838541</v>
+        <v>21.8362582020052</v>
       </c>
       <c r="D48" t="n">
-        <v>23.38275474563442</v>
+        <v>14.9065455743625</v>
       </c>
     </row>
     <row r="49">
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>25.49574603119791</v>
+        <v>22.59106553132812</v>
       </c>
       <c r="D49" t="n">
-        <v>18.50533493066776</v>
+        <v>5.569891985829821</v>
       </c>
     </row>
     <row r="50">
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>22.87593293958333</v>
+        <v>10.79133533869047</v>
       </c>
       <c r="D50" t="n">
-        <v>27.96622670347083</v>
+        <v>6.932797600311041</v>
       </c>
     </row>
     <row r="51">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>19.32193036094979</v>
+        <v>9.859975012814164</v>
       </c>
       <c r="D51" t="n">
-        <v>19.49565637680229</v>
+        <v>8.533409703848447</v>
       </c>
     </row>
     <row r="52">
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38.07399731597087</v>
+        <v>97.92657368990524</v>
       </c>
       <c r="D52" t="n">
-        <v>21.78829090448018</v>
+        <v>50.36669548553899</v>
       </c>
     </row>
   </sheetData>
@@ -2093,25 +2093,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>93.41397849462365</v>
+        <v>87.09677419354838</v>
       </c>
       <c r="D2" t="n">
-        <v>48.11827956989247</v>
+        <v>27.68817204301075</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6315855037016905</v>
+        <v>0.4888750164524106</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5156172261755152</v>
+        <v>0.8096376506933244</v>
       </c>
       <c r="G2" t="n">
-        <v>0.145497311827957</v>
+        <v>0.1785394265232975</v>
       </c>
       <c r="H2" t="n">
-        <v>87.4074074074074</v>
+        <v>45.33678756476684</v>
       </c>
       <c r="I2" t="n">
-        <v>98.23008849557522</v>
+        <v>93.85474860335195</v>
       </c>
     </row>
     <row r="3">
@@ -2126,25 +2126,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>88.97849462365592</v>
+        <v>83.87096774193549</v>
       </c>
       <c r="D3" t="n">
-        <v>43.27956989247312</v>
+        <v>29.83870967741936</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5304688706970864</v>
+        <v>0.3907279004343125</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8020188521852598</v>
+        <v>0.855227870109207</v>
       </c>
       <c r="G3" t="n">
-        <v>0.15165770609319</v>
+        <v>0.1962365591397849</v>
       </c>
       <c r="H3" t="n">
-        <v>79.50617283950618</v>
+        <v>49.74093264248705</v>
       </c>
       <c r="I3" t="n">
-        <v>97.34513274336283</v>
+        <v>91.62011173184358</v>
       </c>
     </row>
     <row r="4">
@@ -2159,25 +2159,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>89.11290322580645</v>
+        <v>90.32258064516128</v>
       </c>
       <c r="D4" t="n">
-        <v>41.53225806451613</v>
+        <v>32.5268817204301</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5437946142160245</v>
+        <v>0.5078169264641724</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7697497367299507</v>
+        <v>0.8260861749882393</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1723790322580645</v>
+        <v>0.1816756272401434</v>
       </c>
       <c r="H4" t="n">
-        <v>74.75490196078431</v>
+        <v>54.24164524421594</v>
       </c>
       <c r="I4" t="n">
-        <v>98.80952380952381</v>
+        <v>95.49295774647887</v>
       </c>
     </row>
     <row r="5">
@@ -2192,25 +2192,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>94.08602150537635</v>
+        <v>86.69354838709677</v>
       </c>
       <c r="D5" t="n">
-        <v>49.86559139784946</v>
+        <v>23.65591397849462</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6648991144445189</v>
+        <v>0.4622690160936668</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2964989051299283</v>
+        <v>0.545427688172043</v>
       </c>
       <c r="G5" t="n">
-        <v>0.12959229390681</v>
+        <v>0.1868279569892473</v>
       </c>
       <c r="H5" t="n">
-        <v>88.64734299516908</v>
+        <v>35.5</v>
       </c>
       <c r="I5" t="n">
-        <v>99.39393939393939</v>
+        <v>96.22093023255815</v>
       </c>
     </row>
     <row r="6">
@@ -2225,25 +2225,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>93.01075268817203</v>
+        <v>84.00537634408603</v>
       </c>
       <c r="D6" t="n">
-        <v>48.65591397849462</v>
+        <v>26.61290322580645</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5813181133902368</v>
+        <v>0.3384655795441547</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4695727472558243</v>
+        <v>0.5327753864247312</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1265681003584229</v>
+        <v>0.2019489247311828</v>
       </c>
       <c r="H6" t="n">
-        <v>87.19806763285024</v>
+        <v>42.25</v>
       </c>
       <c r="I6" t="n">
-        <v>99.09090909090909</v>
+        <v>95.93023255813954</v>
       </c>
     </row>
     <row r="7">
@@ -2258,25 +2258,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>91.93548387096774</v>
+        <v>87.63440860215054</v>
       </c>
       <c r="D7" t="n">
-        <v>45.83333333333333</v>
+        <v>30.51075268817204</v>
       </c>
       <c r="E7" t="n">
-        <v>0.587997359713606</v>
+        <v>0.4974976082915729</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5223238701276881</v>
+        <v>0.5165386648745519</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1508736559139785</v>
+        <v>0.1782034050179211</v>
       </c>
       <c r="H7" t="n">
-        <v>81.20481927710843</v>
+        <v>46.51741293532339</v>
       </c>
       <c r="I7" t="n">
-        <v>99.69604863221885</v>
+        <v>96.78362573099415</v>
       </c>
     </row>
     <row r="8">
@@ -2291,25 +2291,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>89.86111111111111</v>
+        <v>82.91666666666667</v>
       </c>
       <c r="D8" t="n">
-        <v>87.5</v>
+        <v>75.13888888888889</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2075186742837069</v>
+        <v>0.3094145160246225</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07813968990393517</v>
+        <v>0.2361147665381944</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0212962962962963</v>
+        <v>0.06319444444444444</v>
       </c>
       <c r="H8" t="n">
-        <v>88.68715083798882</v>
+        <v>75.52447552447552</v>
       </c>
       <c r="I8" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9">
@@ -2324,25 +2324,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>85.55555555555556</v>
+        <v>88.47222222222221</v>
       </c>
       <c r="D9" t="n">
-        <v>83.33333333333334</v>
+        <v>82.5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.179646341201129</v>
+        <v>0.4250229195760289</v>
       </c>
       <c r="F9" t="n">
-        <v>0.207387583912037</v>
+        <v>0.114310069400463</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02939814814814815</v>
+        <v>0.03576388888888889</v>
       </c>
       <c r="H9" t="n">
-        <v>84.07821229050279</v>
+        <v>82.23776223776224</v>
       </c>
       <c r="I9" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
@@ -2357,22 +2357,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>84.02777777777779</v>
+        <v>88.33333333333333</v>
       </c>
       <c r="D10" t="n">
-        <v>77.91666666666667</v>
+        <v>77.08333333333334</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08985190368335109</v>
+        <v>0.3846656514438569</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2457041864317129</v>
+        <v>0.2209661332581019</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03912037037037037</v>
+        <v>0.06145833333333333</v>
       </c>
       <c r="H10" t="n">
-        <v>79.05027932960894</v>
+        <v>76.22377622377621</v>
       </c>
       <c r="I10" t="n">
         <v>100</v>
@@ -2449,25 +2449,25 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>26.61290322580645</v>
+        <v>28.36021505376344</v>
       </c>
       <c r="D2" t="n">
-        <v>263.939575</v>
+        <v>328.9534857142857</v>
       </c>
       <c r="E2" t="n">
-        <v>8.182000000000002</v>
+        <v>9.775675</v>
       </c>
       <c r="F2" t="n">
-        <v>2.469135802469136</v>
+        <v>44.55958549222798</v>
       </c>
       <c r="G2" t="n">
-        <v>2.023121387283237</v>
+        <v>11.56862745098039</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -2480,25 +2480,25 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>26.20967741935484</v>
+        <v>25.67204301075269</v>
       </c>
       <c r="D3" t="n">
-        <v>260.288175</v>
+        <v>245.8346464285715</v>
       </c>
       <c r="E3" t="n">
-        <v>7.7394</v>
+        <v>8.261150000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>11.51960784313725</v>
+        <v>43.95886889460154</v>
       </c>
       <c r="G3" t="n">
-        <v>8.136482939632545</v>
+        <v>10.03861003861004</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -2511,25 +2511,25 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>24.86559139784946</v>
+        <v>29.97311827956989</v>
       </c>
       <c r="D4" t="n">
-        <v>259.298075</v>
+        <v>323.3304142857143</v>
       </c>
       <c r="E4" t="n">
-        <v>9.009125000000001</v>
+        <v>8.247425</v>
       </c>
       <c r="F4" t="n">
-        <v>19.559902200489</v>
+        <v>31.18556701030928</v>
       </c>
       <c r="G4" t="n">
-        <v>6.796116504854369</v>
+        <v>5.387931034482759</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -2542,25 +2542,25 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>22.04301075268817</v>
+        <v>20.43010752688172</v>
       </c>
       <c r="D5" t="n">
-        <v>194.2516000000001</v>
+        <v>221.119275</v>
       </c>
       <c r="E5" t="n">
-        <v>5.338825</v>
+        <v>6.004425000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>1.449275362318841</v>
+        <v>54.25</v>
       </c>
       <c r="G5" t="n">
-        <v>1.492537313432836</v>
+        <v>16.48550724637681</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -2573,25 +2573,25 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>19.48924731182796</v>
+        <v>17.33870967741936</v>
       </c>
       <c r="D6" t="n">
-        <v>147.04285</v>
+        <v>145.8716107142857</v>
       </c>
       <c r="E6" t="n">
-        <v>5.088075</v>
+        <v>5.620975</v>
       </c>
       <c r="F6" t="n">
-        <v>11.08433734939759</v>
+        <v>51.99004975124378</v>
       </c>
       <c r="G6" t="n">
-        <v>9.066666666666666</v>
+        <v>13.02752293577982</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -2604,25 +2604,25 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>17.74193548387097</v>
+        <v>23.25268817204301</v>
       </c>
       <c r="D7" t="n">
-        <v>161.449425</v>
+        <v>206.057325</v>
       </c>
       <c r="E7" t="n">
-        <v>5.373699999999999</v>
+        <v>5.734375</v>
       </c>
       <c r="F7" t="n">
-        <v>12.07729468599034</v>
+        <v>33.16708229426434</v>
       </c>
       <c r="G7" t="n">
-        <v>5.54089709762533</v>
+        <v>7.67590618336887</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -2635,19 +2635,19 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="D8" t="n">
-        <v>1.88325</v>
+        <v>5.585700000000004</v>
       </c>
       <c r="E8" t="n">
-        <v>1.88325</v>
+        <v>2.392100000000003</v>
       </c>
       <c r="F8" t="n">
-        <v>1.955307262569832</v>
+        <v>10.06993006993007</v>
       </c>
       <c r="G8" t="n">
-        <v>72.22222222222223</v>
+        <v>86.84210526315789</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -2669,16 +2669,16 @@
         <v>0.1388888888888889</v>
       </c>
       <c r="D9" t="n">
-        <v>2.274950000000002</v>
+        <v>1.369100000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>2.274950000000002</v>
+        <v>1.369100000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>10.47486033519553</v>
+        <v>21.81818181818182</v>
       </c>
       <c r="G9" t="n">
-        <v>91.13924050632912</v>
+        <v>88.81987577639751</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -2697,19 +2697,19 @@
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="D10" t="n">
-        <v>1.939175000000001</v>
+        <v>2.793824999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>1.939175000000001</v>
+        <v>1.995100000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>15.36312849162011</v>
+        <v>13.98601398601399</v>
       </c>
       <c r="G10" t="n">
-        <v>92.10526315789474</v>
+        <v>89.52380952380952</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -2754,10 +2754,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2" t="n">
-        <v>82</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3">
@@ -2768,7 +2768,7 @@
         <v>65</v>
       </c>
       <c r="C3" t="n">
-        <v>91</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4">
@@ -2779,7 +2779,7 @@
         <v>65</v>
       </c>
       <c r="C4" t="n">
-        <v>82</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
